--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N115_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N115_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.34709662169833</v>
+        <v>4.443903201025979</v>
       </c>
       <c r="D2" t="n">
-        <v>28.99426003003241</v>
+        <v>4.711567254880267</v>
       </c>
       <c r="E2" t="n">
-        <v>13.10445347366411</v>
+        <v>2.129473689470418</v>
       </c>
       <c r="F2" t="n">
-        <v>13.28407000312366</v>
+        <v>2.158661375507595</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.59982311999849</v>
+        <v>5.134971256999755</v>
       </c>
       <c r="D3" t="n">
-        <v>32.37087661862941</v>
+        <v>5.260267450527279</v>
       </c>
       <c r="E3" t="n">
-        <v>13.10445347366411</v>
+        <v>2.129473689470418</v>
       </c>
       <c r="F3" t="n">
-        <v>13.28407000312366</v>
+        <v>2.158661375507595</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.26912599458</v>
+        <v>6.868732974119251</v>
       </c>
       <c r="D4" t="n">
-        <v>43.3240118179284</v>
+        <v>7.040151920413366</v>
       </c>
       <c r="E4" t="n">
-        <v>13.10445347366411</v>
+        <v>2.129473689470418</v>
       </c>
       <c r="F4" t="n">
-        <v>13.28407000312366</v>
+        <v>2.158661375507595</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.68336553417684</v>
+        <v>7.098546899303736</v>
       </c>
       <c r="D5" t="n">
-        <v>43.03011274213017</v>
+        <v>6.992393320596153</v>
       </c>
       <c r="E5" t="n">
-        <v>13.10445347366411</v>
+        <v>2.129473689470418</v>
       </c>
       <c r="F5" t="n">
-        <v>13.28407000312366</v>
+        <v>2.158661375507595</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.76060576217587</v>
+        <v>5.648598436353579</v>
       </c>
       <c r="D6" t="n">
-        <v>32.57383919723548</v>
+        <v>5.293248869550766</v>
       </c>
       <c r="E6" t="n">
-        <v>13.10445347366411</v>
+        <v>2.129473689470418</v>
       </c>
       <c r="F6" t="n">
-        <v>13.28407000312366</v>
+        <v>2.158661375507595</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.99049464481122</v>
+        <v>2.435955379781823</v>
       </c>
       <c r="D7" t="n">
-        <v>13.8670830352731</v>
+        <v>2.253400993231879</v>
       </c>
       <c r="E7" t="n">
-        <v>13.10445347366411</v>
+        <v>2.129473689470418</v>
       </c>
       <c r="F7" t="n">
-        <v>13.28407000312366</v>
+        <v>2.158661375507595</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.52598018633625</v>
+        <v>2.847971780279641</v>
       </c>
       <c r="D8" t="n">
-        <v>17.6350126854469</v>
+        <v>2.865689561385122</v>
       </c>
       <c r="E8" t="n">
-        <v>13.10445347366411</v>
+        <v>2.129473689470418</v>
       </c>
       <c r="F8" t="n">
-        <v>13.28407000312366</v>
+        <v>2.158661375507595</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.71912499400019</v>
+        <v>1.904357811525031</v>
       </c>
       <c r="D9" t="n">
-        <v>10.80725133276081</v>
+        <v>1.756178341573631</v>
       </c>
       <c r="E9" t="n">
-        <v>13.10445347366411</v>
+        <v>2.129473689470418</v>
       </c>
       <c r="F9" t="n">
-        <v>13.28407000312366</v>
+        <v>2.158661375507595</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4.439920114709272</v>
+        <v>0.7214870186402568</v>
       </c>
       <c r="D10" t="n">
-        <v>4.492297779586153</v>
+        <v>0.7299983891827498</v>
       </c>
       <c r="E10" t="n">
-        <v>13.10445347366411</v>
+        <v>2.129473689470418</v>
       </c>
       <c r="F10" t="n">
-        <v>13.28407000312366</v>
+        <v>2.158661375507595</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
